--- a/data/trans_orig/P3A$yo-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P3A$yo-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>196451</t>
+          <t>199296</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>161492</t>
+          <t>164597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>231365</t>
+          <t>230305</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>211927</t>
+          <t>247501</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>187793</t>
+          <t>220076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>234205</t>
+          <t>270228</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>408377</t>
+          <t>446798</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>367899</t>
+          <t>406066</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>450402</t>
+          <t>493800</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>64,1%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25580</t>
+          <t>25918</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13062</t>
+          <t>13048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47494</t>
+          <t>48392</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31240</t>
+          <t>32657</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19849</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45433</t>
+          <t>49494</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>56820</t>
+          <t>58575</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39984</t>
+          <t>41524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79396</t>
+          <t>82249</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>323058</t>
+          <t>318476</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>289803</t>
+          <t>288275</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>346683</t>
+          <t>340539</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>249299</t>
+          <t>287792</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>229146</t>
+          <t>269208</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>264792</t>
+          <t>304830</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>572356</t>
+          <t>606267</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>539623</t>
+          <t>567956</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>603343</t>
+          <t>636811</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30972</t>
+          <t>16442</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34107</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29090</t>
+          <t>29230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>15911</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33408</t>
+          <t>33855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19795</t>
+          <t>14375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,32 +1438,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20785</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>13897</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27514</t>
+          <t>29587</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>285935</t>
+          <t>313266</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>262396</t>
+          <t>283993</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310726</t>
+          <t>339440</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>479432</t>
+          <t>465725</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>463617</t>
+          <t>447471</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>492918</t>
+          <t>477102</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>765367</t>
+          <t>778991</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>729196</t>
+          <t>743018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>806067</t>
+          <t>807527</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>160036</t>
+          <t>177539</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>136686</t>
+          <t>150506</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>184269</t>
+          <t>205736</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>117789</t>
+          <t>127206</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>69644</t>
+          <t>108431</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145700</t>
+          <t>147561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>277825</t>
+          <t>304745</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>210066</t>
+          <t>272515</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>317485</t>
+          <t>341304</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>172620</t>
+          <t>200368</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>146184</t>
+          <t>171742</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>197591</t>
+          <t>231255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>147579</t>
+          <t>158695</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89448</t>
+          <t>136553</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>179144</t>
+          <t>181314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>320199</t>
+          <t>359064</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>246641</t>
+          <t>321818</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>362017</t>
+          <t>394749</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>9279</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>929</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12243</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,22 +2042,22 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11236</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2095,12 +2095,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>22625</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19787</t>
+          <t>22734</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>26772</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>413336</t>
+          <t>468248</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>393380</t>
+          <t>443059</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>433318</t>
+          <t>490534</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>576164</t>
+          <t>604805</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>569197</t>
+          <t>596453</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>582220</t>
+          <t>610883</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>989500</t>
+          <t>1073052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>965844</t>
+          <t>1047200</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1016498</t>
+          <t>1096373</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>88,13%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>324125</t>
+          <t>381215</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>300423</t>
+          <t>355341</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>348316</t>
+          <t>405793</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>207944</t>
+          <t>228978</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>157543</t>
+          <t>208920</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>233835</t>
+          <t>252529</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>532068</t>
+          <t>610192</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>464963</t>
+          <t>575485</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>572237</t>
+          <t>643747</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>107351</t>
+          <t>118120</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88048</t>
+          <t>98617</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126021</t>
+          <t>139159</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>138573</t>
+          <t>101660</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>93050</t>
+          <t>86631</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256779</t>
+          <t>116701</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>245923</t>
+          <t>219780</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>196171</t>
+          <t>197865</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>370671</t>
+          <t>247874</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5830</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10028</t>
+          <t>11435</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15673</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>6701</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>12253</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>15496</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>9223</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22746</t>
+          <t>24339</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>710</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,22 +2950,22 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>711</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8402</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -2993,67 +2993,67 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15066</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>6010</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2920</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>11687</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>5193</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2215</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>10817</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>13228</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21021</t>
+          <t>21976</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>468927</t>
+          <t>507007</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>196737</t>
+          <t>481908</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>656396</t>
+          <t>531551</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>693913</t>
+          <t>716572</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>685192</t>
+          <t>708240</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>699957</t>
+          <t>722718</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1162839</t>
+          <t>1223579</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>759757</t>
+          <t>1196863</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1382062</t>
+          <t>1248688</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,91%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>356045</t>
+          <t>395618</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>157510</t>
+          <t>369479</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>504266</t>
+          <t>424252</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>207519</t>
+          <t>220194</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>175885</t>
+          <t>202598</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>230836</t>
+          <t>241569</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>563564</t>
+          <t>615812</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>362305</t>
+          <t>582469</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>685955</t>
+          <t>653757</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>45,5%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>117100</t>
+          <t>129634</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>47921</t>
+          <t>110248</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>171445</t>
+          <t>151567</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>166884</t>
+          <t>180421</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>138893</t>
+          <t>163971</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>187909</t>
+          <t>200625</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>283984</t>
+          <t>310055</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>181069</t>
+          <t>281117</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>348949</t>
+          <t>337102</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>11717</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21967</t>
+          <t>20525</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>15281</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>9226</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24747</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>11927</t>
+          <t>13838</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22163</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24232</t>
+          <t>24321</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>28810</t>
+          <t>31160</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>21552</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41542</t>
+          <t>42618</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14183</t>
+          <t>13623</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>9816</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17620</t>
+          <t>18424</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -3788,32 +3788,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>251021</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>618083</t>
+          <t>15823</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3823,32 +3823,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3858,32 +3858,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>253644</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>689507</t>
+          <t>19307</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>386377</t>
+          <t>418530</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>398525</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>408419</t>
+          <t>441204</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>531277</t>
+          <t>590445</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>524057</t>
+          <t>582729</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>536275</t>
+          <t>596311</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>917654</t>
+          <t>1008976</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>892336</t>
+          <t>983837</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>938071</t>
+          <t>1031072</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>334610</t>
+          <t>365316</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>312652</t>
+          <t>341037</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>356061</t>
+          <t>386440</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>120643</t>
+          <t>134914</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>106914</t>
+          <t>118401</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>135433</t>
+          <t>151818</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>455252</t>
+          <t>500230</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>428440</t>
+          <t>471013</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>483340</t>
+          <t>529101</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,43%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>112566</t>
+          <t>121542</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>96681</t>
+          <t>103041</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>131233</t>
+          <t>141740</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>90325</t>
+          <t>99785</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>77963</t>
+          <t>87230</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>102371</t>
+          <t>114979</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>202891</t>
+          <t>221327</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>181854</t>
+          <t>197082</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>225080</t>
+          <t>244086</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16135</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>12797</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>20454</t>
+          <t>21407</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13263</t>
+          <t>14762</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28820</t>
+          <t>30097</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -4357,22 +4357,22 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>18186</t>
+          <t>18078</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7088</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>18659</t>
+          <t>18543</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>22128</t>
+          <t>23172</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>15357</t>
+          <t>15880</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>30441</t>
+          <t>32785</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -4470,22 +4470,22 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>16598</t>
+          <t>17708</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>12514</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>19045</t>
+          <t>21742</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -4583,32 +4583,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4618,32 +4618,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4653,32 +4653,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>10638</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>230492</t>
+          <t>253943</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>215662</t>
+          <t>235926</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>245997</t>
+          <t>270386</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>586226</t>
+          <t>413444</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>572028</t>
+          <t>405232</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>599535</t>
+          <t>420071</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>816720</t>
+          <t>667387</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>767722</t>
+          <t>646259</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>896448</t>
+          <t>685323</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>81,14%</t>
         </is>
       </c>
     </row>
@@ -4813,32 +4813,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>217787</t>
+          <t>241946</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>201801</t>
+          <t>225195</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>232751</t>
+          <t>257665</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>55392</t>
+          <t>60265</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>20495</t>
+          <t>50723</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>88584</t>
+          <t>71762</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>273179</t>
+          <t>302211</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>133725</t>
+          <t>280475</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>353622</t>
+          <t>326061</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -4926,32 +4926,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>47206</t>
+          <t>52489</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>36966</t>
+          <t>42192</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>57740</t>
+          <t>64757</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4961,32 +4961,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>46225</t>
+          <t>50795</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>19591</t>
+          <t>42250</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>73746</t>
+          <t>61060</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>93431</t>
+          <t>103284</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>41911</t>
+          <t>89477</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>122370</t>
+          <t>119195</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -5039,32 +5039,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>13664</t>
+          <t>14527</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8607</t>
+          <t>9574</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>20955</t>
+          <t>22265</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>25553</t>
+          <t>27216</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>20399</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>42788</t>
+          <t>35129</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>39217</t>
+          <t>41743</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>32118</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>54068</t>
+          <t>51599</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -5152,22 +5152,22 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>19790</t>
+          <t>21841</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>13627</t>
+          <t>15051</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>27234</t>
+          <t>30592</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,32 +5187,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>20851</t>
+          <t>24436</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>18224</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>35011</t>
+          <t>32504</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>40642</t>
+          <t>46278</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>20359</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>56376</t>
+          <t>57855</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -5265,67 +5265,67 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>12136</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>10766</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>6687</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>15982</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>9686</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>3146</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>16588</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>15267</t>
+          <t>16895</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>11359</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>22931</t>
+          <t>24260</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -5378,32 +5378,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5413,32 +5413,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>429</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5448,32 +5448,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>12031</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -5495,32 +5495,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>139089</t>
+          <t>152265</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>125844</t>
+          <t>137584</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>151896</t>
+          <t>166606</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,32 +5530,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>318639</t>
+          <t>347432</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>304700</t>
+          <t>334065</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>331225</t>
+          <t>362194</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>457728</t>
+          <t>499697</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>438262</t>
+          <t>476679</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>477248</t>
+          <t>519632</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -5608,32 +5608,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>136768</t>
+          <t>150566</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>124400</t>
+          <t>135422</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>150233</t>
+          <t>165541</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5643,32 +5643,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>25245</t>
+          <t>27125</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>19513</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>32613</t>
+          <t>35120</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>162013</t>
+          <t>177691</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>143635</t>
+          <t>160887</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>177990</t>
+          <t>199710</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -5721,32 +5721,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>30458</t>
+          <t>33504</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>22459</t>
+          <t>24851</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>38544</t>
+          <t>42938</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5756,32 +5756,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>64173</t>
+          <t>69775</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>54222</t>
+          <t>59276</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>75394</t>
+          <t>81800</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>94631</t>
+          <t>103279</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>82053</t>
+          <t>88945</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>109375</t>
+          <t>118786</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -5834,32 +5834,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>61379</t>
+          <t>64691</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>50720</t>
+          <t>53061</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>72747</t>
+          <t>76864</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5869,32 +5869,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>99397</t>
+          <t>106693</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>87711</t>
+          <t>93849</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>111177</t>
+          <t>119888</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>160776</t>
+          <t>171384</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>144921</t>
+          <t>155221</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>176493</t>
+          <t>189066</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5947,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>34134</t>
+          <t>37343</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>26307</t>
+          <t>29364</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>42804</t>
+          <t>47914</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5982,32 +5982,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>60914</t>
+          <t>68568</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>72842</t>
+          <t>81396</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>95047</t>
+          <t>105911</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>82039</t>
+          <t>91843</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>109375</t>
+          <t>121495</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>31175</t>
+          <t>33280</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>23781</t>
+          <t>25092</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>40403</t>
+          <t>43045</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6095,32 +6095,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>64584</t>
+          <t>68847</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>55134</t>
+          <t>58233</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>75427</t>
+          <t>80626</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>95758</t>
+          <t>102128</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>83354</t>
+          <t>88049</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>110533</t>
+          <t>115676</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>5679</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6208,32 +6208,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6243,27 +6243,27 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>10082</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>2120608</t>
+          <t>2312557</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>1616269</t>
+          <t>2251481</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2302431</t>
+          <t>2374350</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6325,32 +6325,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>3397577</t>
+          <t>3385923</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>3353826</t>
+          <t>3345644</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3455773</t>
+          <t>3421280</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6360,32 +6360,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>5518185</t>
+          <t>5698481</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>4883769</t>
+          <t>5618246</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>5758566</t>
+          <t>5775071</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -6403,32 +6403,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1554951</t>
+          <t>1738118</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1192592</t>
+          <t>1665820</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1700703</t>
+          <t>1796052</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6438,32 +6438,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>765770</t>
+          <t>831338</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>614292</t>
+          <t>786819</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>843229</t>
+          <t>873757</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6473,32 +6473,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>2320721</t>
+          <t>2569457</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>2016671</t>
+          <t>2485627</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2492035</t>
+          <t>2654563</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -6516,32 +6516,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>910358</t>
+          <t>974134</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>712530</t>
+          <t>911085</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1001359</t>
+          <t>1044348</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>903057</t>
+          <t>948922</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>737230</t>
+          <t>897206</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1025692</t>
+          <t>1004927</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>1813415</t>
+          <t>1923057</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1611652</t>
+          <t>1834414</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1974983</t>
+          <t>2009994</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -6629,32 +6629,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>105125</t>
+          <t>106749</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>79067</t>
+          <t>88936</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>129235</t>
+          <t>127027</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6664,32 +6664,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>146841</t>
+          <t>158638</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>117353</t>
+          <t>140113</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>167125</t>
+          <t>177963</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>251965</t>
+          <t>265387</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>209298</t>
+          <t>241658</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>283026</t>
+          <t>293041</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -6742,32 +6742,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>95211</t>
+          <t>103927</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>72969</t>
+          <t>85939</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>117979</t>
+          <t>127884</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6777,32 +6777,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>123885</t>
+          <t>137872</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>99331</t>
+          <t>118070</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>143985</t>
+          <t>156332</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>219096</t>
+          <t>241799</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>186252</t>
+          <t>215168</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>253087</t>
+          <t>268184</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6855,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>57508</t>
+          <t>61849</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>42948</t>
+          <t>49532</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>74293</t>
+          <t>79977</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6890,32 +6890,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>82512</t>
+          <t>88518</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>67461</t>
+          <t>76532</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>98508</t>
+          <t>104053</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>140020</t>
+          <t>150367</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>118415</t>
+          <t>130647</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>162345</t>
+          <t>170365</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -6968,32 +6968,32 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>277420</t>
+          <t>37304</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>30528</t>
+          <t>26808</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1057929</t>
+          <t>54994</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7003,32 +7003,32 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>26594</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>22608</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>40858</t>
+          <t>47478</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7038,32 +7038,32 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>304014</t>
+          <t>70628</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>54832</t>
+          <t>54393</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>1050624</t>
+          <t>92180</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
